--- a/packages/calculators/src/modules/test/8.1-transport-fuel.xlsx
+++ b/packages/calculators/src/modules/test/8.1-transport-fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7F3E72-EF86-CB4F-AB39-2B1640BBBF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AA7B24-05AC-454A-AA21-C567261DF5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="17340" windowWidth="28800" windowHeight="23520" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="51140" yWindow="5260" windowWidth="28800" windowHeight="18980" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="8.1.1.1" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="63">
   <si>
     <t>Method 1</t>
   </si>
@@ -253,9 +253,6 @@
     <t>Scope 3 EF (kg CO2-e/GJ)</t>
   </si>
   <si>
-    <t>Amount of fuel combusted kL</t>
-  </si>
-  <si>
     <t>EC units</t>
   </si>
   <si>
@@ -377,14 +374,33 @@
   <si>
     <t>Test inputs with no scope 3 factor (skipped for now)</t>
   </si>
+  <si>
+    <t>Eftrans combined</t>
+  </si>
+  <si>
+    <t>Eg combined</t>
+  </si>
+  <si>
+    <t>Amount of fuel combusted kL or cubic metre</t>
+  </si>
+  <si>
+    <t>GWP</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>N2O</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -470,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -498,7 +514,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -852,7 +869,7 @@
     <col min="22" max="22" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17">
+    <row r="1" spans="1:18" ht="17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -860,9 +877,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="34">
+    <row r="3" spans="1:18" ht="51">
       <c r="C3" s="7" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>6</v>
@@ -875,12 +892,12 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="17">
+    <row r="4" spans="1:18" ht="17">
       <c r="A4" s="13" t="s">
         <v>11</v>
       </c>
@@ -894,7 +911,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>7</v>
@@ -906,24 +923,29 @@
         <v>9</v>
       </c>
       <c r="I4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" s="17"/>
+      <c r="N4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -953,29 +975,39 @@
         <f>IF(ISBLANK(E5), "", VLOOKUP($B5, _xlfn.IFS($A5="Cars and light commercial vehicles", $P$36:$W$43,$A5="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A5="Light duty vehicles",$P$49:$W$50,$A5="Heavy duty vehicles",$P$51:$W$58,$A5="Aviation",$P$59:$W$61,$A5="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
         <v>0.2</v>
       </c>
-      <c r="I5" s="12">
-        <f>IF(ISBLANK(F5), "", VLOOKUP($B5, _xlfn.IFS($A5="Cars and light commercial vehicles", $P$36:$W$43,$A5="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A5="Light duty vehicles",$P$49:$W$50,$A5="Heavy duty vehicles",$P$51:$W$58,$A5="Aviation",$P$59:$W$61,$A5="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I5">
+        <f>IF(ISBLANK(E5), "", VLOOKUP($B5, _xlfn.IFS($A5="Cars and light commercial vehicles", $P$36:$W$43,$A5="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A5="Light duty vehicles",$P$49:$W$50,$A5="Heavy duty vehicles",$P$51:$W$58,$A5="Aviation",$P$59:$W$61,$A5="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),7,FALSE))</f>
+        <v>67.62</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" ref="J5:J22" si="0">IF(ISBLANK(F5), "", VLOOKUP($B5, _xlfn.IFS($A5="Cars and light commercial vehicles", $P$36:$W$43,$A5="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A5="Light duty vehicles",$P$49:$W$50,$A5="Heavy duty vehicles",$P$51:$W$58,$A5="Aviation",$P$59:$W$61,$A5="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
         <v>17.2</v>
       </c>
-      <c r="J5" s="12">
-        <f>C5*D5*F5/1000</f>
+      <c r="K5" s="12">
+        <f t="shared" ref="K5:K22" si="1">C5*D5*F5/1000</f>
         <v>11.525400000000001</v>
       </c>
-      <c r="K5" s="12">
-        <f>C5*D5*G5/1000</f>
-        <v>3.4199999999999999E-3</v>
-      </c>
-      <c r="L5" s="12">
-        <f>C5*D5*H5/1000</f>
-        <v>3.4200000000000001E-2</v>
-      </c>
-      <c r="M5" s="12">
+      <c r="L5" s="18">
+        <f>(C5*D5*G5 / $R$6)/1000</f>
+        <v>1.2214285714285715E-4</v>
+      </c>
+      <c r="M5" s="18">
+        <f>(C5*D5*H5/$R$7)/1000</f>
+        <v>1.290566037735849E-4</v>
+      </c>
+      <c r="N5" s="12">
         <f>C5*D5*I5/1000</f>
+        <v>11.56302</v>
+      </c>
+      <c r="O5" s="12">
+        <f t="shared" ref="O5:O22" si="2">C5*D5*J5/1000</f>
         <v>2.9411999999999998</v>
       </c>
-      <c r="N5" s="12"/>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="Q5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -986,48 +1018,61 @@
         <v>6</v>
       </c>
       <c r="D6" s="12">
-        <f t="shared" ref="D6:D12" si="0">IF(ISBLANK(A6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" ref="D6:D8" si="3">IF(ISBLANK(A6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
         <v>38.6</v>
       </c>
       <c r="E6" s="12" t="str">
-        <f t="shared" ref="E6:E12" si="1">IF(ISBLANK(B6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" ref="E6:E8" si="4">IF(ISBLANK(B6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
         <v>GJ/kL</v>
       </c>
       <c r="F6" s="12">
-        <f t="shared" ref="F6:F12" si="2">IF(ISBLANK(C6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" ref="F6:F8" si="5">IF(ISBLANK(C6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
         <v>69.900000000000006</v>
       </c>
       <c r="G6" s="12">
-        <f t="shared" ref="G6:G12" si="3">IF(ISBLANK(D6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" ref="G6:G8" si="6">IF(ISBLANK(D6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
         <v>0.01</v>
       </c>
       <c r="H6" s="12">
-        <f t="shared" ref="H6:H12" si="4">IF(ISBLANK(E6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" ref="H6:H8" si="7">IF(ISBLANK(E6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
         <v>0.5</v>
       </c>
-      <c r="I6" s="12">
-        <f t="shared" ref="I6:I30" si="5">IF(ISBLANK(F6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I6">
+        <f t="shared" ref="I6:I22" si="8">IF(ISBLANK(E6), "", VLOOKUP($B6, _xlfn.IFS($A6="Cars and light commercial vehicles", $P$36:$W$43,$A6="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A6="Light duty vehicles",$P$49:$W$50,$A6="Heavy duty vehicles",$P$51:$W$58,$A6="Aviation",$P$59:$W$61,$A6="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),7,FALSE))</f>
+        <v>70.41</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
-      <c r="J6" s="12">
-        <f t="shared" ref="J6:J12" si="6">C6*D6*F6/1000</f>
+      <c r="K6" s="12">
+        <f t="shared" si="1"/>
         <v>16.188840000000003</v>
       </c>
-      <c r="K6" s="12">
-        <f t="shared" ref="K6:K12" si="7">C6*D6*G6/1000</f>
-        <v>2.3160000000000004E-3</v>
-      </c>
-      <c r="L6" s="12">
-        <f t="shared" ref="L6:L12" si="8">C6*D6*H6/1000</f>
-        <v>0.11580000000000001</v>
-      </c>
-      <c r="M6" s="12">
-        <f t="shared" ref="M6:M30" si="9">C6*D6*I6/1000</f>
+      <c r="L6" s="18">
+        <f t="shared" ref="L6:L22" si="9">(C6*D6*G6 / $R$6)/1000</f>
+        <v>8.2714285714285721E-5</v>
+      </c>
+      <c r="M6" s="18">
+        <f t="shared" ref="M6:M22" si="10">(C6*D6*H6/$R$7)/1000</f>
+        <v>4.3698113207547173E-4</v>
+      </c>
+      <c r="N6" s="12">
+        <f t="shared" ref="N6:N22" si="11">C6*D6*I6/1000</f>
+        <v>16.306956</v>
+      </c>
+      <c r="O6" s="12">
+        <f t="shared" si="2"/>
         <v>4.0066800000000011</v>
       </c>
-      <c r="N6" s="12"/>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="Q6" t="s">
+        <v>61</v>
+      </c>
+      <c r="R6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1038,48 +1083,61 @@
         <v>7</v>
       </c>
       <c r="D7" s="12">
+        <f t="shared" si="3"/>
+        <v>26.2</v>
+      </c>
+      <c r="E7" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>GJ/kL</v>
+      </c>
+      <c r="F7" s="12">
+        <f t="shared" si="5"/>
+        <v>60.2</v>
+      </c>
+      <c r="G7" s="12">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="12">
+        <f t="shared" si="7"/>
+        <v>0.3</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="8"/>
+        <v>61</v>
+      </c>
+      <c r="J7" s="12">
         <f t="shared" si="0"/>
-        <v>26.2</v>
-      </c>
-      <c r="E7" s="12" t="str">
+        <v>20.2</v>
+      </c>
+      <c r="K7" s="12">
         <f t="shared" si="1"/>
-        <v>GJ/kL</v>
-      </c>
-      <c r="F7" s="12">
+        <v>11.04068</v>
+      </c>
+      <c r="L7" s="18">
+        <f t="shared" si="9"/>
+        <v>3.2749999999999997E-3</v>
+      </c>
+      <c r="M7" s="18">
+        <f t="shared" si="10"/>
+        <v>2.0762264150943395E-4</v>
+      </c>
+      <c r="N7" s="12">
+        <f t="shared" si="11"/>
+        <v>11.1874</v>
+      </c>
+      <c r="O7" s="12">
         <f t="shared" si="2"/>
-        <v>60.2</v>
-      </c>
-      <c r="G7" s="12">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="12">
-        <f t="shared" si="4"/>
-        <v>0.3</v>
-      </c>
-      <c r="I7" s="12">
-        <f t="shared" si="5"/>
-        <v>20.2</v>
-      </c>
-      <c r="J7" s="12">
-        <f t="shared" si="6"/>
-        <v>11.04068</v>
-      </c>
-      <c r="K7" s="12">
-        <f t="shared" si="7"/>
-        <v>9.1700000000000004E-2</v>
-      </c>
-      <c r="L7" s="12">
-        <f t="shared" si="8"/>
-        <v>5.5020000000000006E-2</v>
-      </c>
-      <c r="M7" s="12">
-        <f t="shared" si="9"/>
         <v>3.7046799999999998</v>
       </c>
-      <c r="N7" s="12"/>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="Q7" t="s">
+        <v>62</v>
+      </c>
+      <c r="R7">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1090,50 +1148,57 @@
         <v>8</v>
       </c>
       <c r="D8" s="12">
+        <f t="shared" si="3"/>
+        <v>39.700000000000003</v>
+      </c>
+      <c r="E8" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>GJ/kL</v>
+      </c>
+      <c r="F8" s="12">
+        <f t="shared" si="5"/>
+        <v>73.599999999999994</v>
+      </c>
+      <c r="G8" s="12">
+        <f t="shared" si="6"/>
+        <v>0.08</v>
+      </c>
+      <c r="H8" s="12">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="8"/>
+        <v>74.180000000000007</v>
+      </c>
+      <c r="J8" s="12">
         <f t="shared" si="0"/>
-        <v>39.700000000000003</v>
-      </c>
-      <c r="E8" s="12" t="str">
+        <v>18</v>
+      </c>
+      <c r="K8" s="12">
         <f t="shared" si="1"/>
-        <v>GJ/kL</v>
-      </c>
-      <c r="F8" s="12">
+        <v>23.375360000000001</v>
+      </c>
+      <c r="L8" s="18">
+        <f t="shared" si="9"/>
+        <v>9.0742857142857151E-4</v>
+      </c>
+      <c r="M8" s="18">
+        <f t="shared" si="10"/>
+        <v>5.9924528301886788E-4</v>
+      </c>
+      <c r="N8" s="12">
+        <f t="shared" si="11"/>
+        <v>23.559568000000002</v>
+      </c>
+      <c r="O8" s="12">
         <f t="shared" si="2"/>
-        <v>73.599999999999994</v>
-      </c>
-      <c r="G8" s="12">
-        <f t="shared" si="3"/>
-        <v>0.08</v>
-      </c>
-      <c r="H8" s="12">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="12">
-        <f t="shared" si="5"/>
-        <v>18</v>
-      </c>
-      <c r="J8" s="12">
-        <f t="shared" si="6"/>
-        <v>23.375360000000001</v>
-      </c>
-      <c r="K8" s="12">
-        <f t="shared" si="7"/>
-        <v>2.5408E-2</v>
-      </c>
-      <c r="L8" s="12">
-        <f t="shared" si="8"/>
-        <v>0.15880000000000002</v>
-      </c>
-      <c r="M8" s="12">
-        <f t="shared" si="9"/>
         <v>5.7168000000000001</v>
       </c>
-      <c r="N8" s="12"/>
-    </row>
-    <row r="9" spans="1:17">
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -1142,47 +1207,55 @@
         <v>4</v>
       </c>
       <c r="D9" s="12">
-        <f>IF(ISBLANK(A9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" ref="D9:D22" si="12">IF(ISBLANK(A9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
         <v>34.200000000000003</v>
       </c>
       <c r="E9" s="12" t="str">
-        <f>IF(ISBLANK(B9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" ref="E9:E22" si="13">IF(ISBLANK(B9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
         <v>GJ/kL</v>
       </c>
       <c r="F9" s="12">
-        <f>IF(ISBLANK(C9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" ref="F9:F22" si="14">IF(ISBLANK(C9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
         <v>67.400000000000006</v>
       </c>
       <c r="G9" s="12">
-        <f>IF(ISBLANK(D9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" ref="G9:G22" si="15">IF(ISBLANK(D9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="H9" s="12">
-        <f>IF(ISBLANK(E9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" ref="H9:H22" si="16">IF(ISBLANK(E9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
         <v>1.6</v>
       </c>
-      <c r="I9" s="12">
-        <f>IF(ISBLANK(F9), "", VLOOKUP($B9, _xlfn.IFS($A9="Cars and light commercial vehicles", $P$36:$W$43,$A9="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A9="Light duty vehicles",$P$49:$W$50,$A9="Heavy duty vehicles",$P$51:$W$58,$A9="Aviation",$P$59:$W$61,$A9="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I9">
+        <f t="shared" si="8"/>
+        <v>69.599999999999994</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="0"/>
         <v>17.2</v>
       </c>
-      <c r="J9" s="12">
-        <f>C9*D9*F9/1000</f>
+      <c r="K9" s="12">
+        <f t="shared" si="1"/>
         <v>9.220320000000001</v>
       </c>
-      <c r="K9" s="12">
-        <f>C9*D9*G9/1000</f>
-        <v>8.208E-2</v>
-      </c>
-      <c r="L9" s="12">
-        <f>C9*D9*H9/1000</f>
-        <v>0.21888000000000002</v>
-      </c>
-      <c r="M9" s="12">
-        <f>C9*D9*I9/1000</f>
+      <c r="L9" s="18">
+        <f t="shared" si="9"/>
+        <v>2.9314285714285714E-3</v>
+      </c>
+      <c r="M9" s="18">
+        <f t="shared" si="10"/>
+        <v>8.2596226415094349E-4</v>
+      </c>
+      <c r="N9" s="12">
+        <f t="shared" si="11"/>
+        <v>9.5212800000000009</v>
+      </c>
+      <c r="O9" s="12">
+        <f t="shared" si="2"/>
         <v>2.3529599999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1193,47 +1266,55 @@
         <v>6</v>
       </c>
       <c r="D10" s="12">
-        <f>IF(ISBLANK(A10), "", VLOOKUP($B10, _xlfn.IFS($A10="Cars and light commercial vehicles", $P$36:$W$43,$A10="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A10="Light duty vehicles",$P$49:$W$50,$A10="Heavy duty vehicles",$P$51:$W$58,$A10="Aviation",$P$59:$W$61,$A10="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>25.3</v>
       </c>
       <c r="E10" s="12" t="str">
-        <f>IF(ISBLANK(B10), "", VLOOKUP($B10, _xlfn.IFS($A10="Cars and light commercial vehicles", $P$36:$W$43,$A10="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A10="Light duty vehicles",$P$49:$W$50,$A10="Heavy duty vehicles",$P$51:$W$58,$A10="Aviation",$P$59:$W$61,$A10="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F10" s="12">
-        <f>IF(ISBLANK(C10), "", VLOOKUP($B10, _xlfn.IFS($A10="Cars and light commercial vehicles", $P$36:$W$43,$A10="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A10="Light duty vehicles",$P$49:$W$50,$A10="Heavy duty vehicles",$P$51:$W$58,$A10="Aviation",$P$59:$W$61,$A10="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>51.4</v>
       </c>
       <c r="G10" s="12">
-        <f>IF(ISBLANK(D10), "", VLOOKUP($B10, _xlfn.IFS($A10="Cars and light commercial vehicles", $P$36:$W$43,$A10="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A10="Light duty vehicles",$P$49:$W$50,$A10="Heavy duty vehicles",$P$51:$W$58,$A10="Aviation",$P$59:$W$61,$A10="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>7.3</v>
       </c>
       <c r="H10" s="12">
-        <f>IF(ISBLANK(E10), "", VLOOKUP($B10, _xlfn.IFS($A10="Cars and light commercial vehicles", $P$36:$W$43,$A10="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A10="Light duty vehicles",$P$49:$W$50,$A10="Heavy duty vehicles",$P$51:$W$58,$A10="Aviation",$P$59:$W$61,$A10="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.3</v>
       </c>
-      <c r="I10" s="12">
-        <f>IF(ISBLANK(F10), "", VLOOKUP($B10, _xlfn.IFS($A10="Cars and light commercial vehicles", $P$36:$W$43,$A10="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A10="Light duty vehicles",$P$49:$W$50,$A10="Heavy duty vehicles",$P$51:$W$58,$A10="Aviation",$P$59:$W$61,$A10="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I10">
+        <f t="shared" si="8"/>
+        <v>59</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="J10" s="12">
-        <f>C10*D10*F10/1000</f>
+      <c r="K10" s="12">
+        <f t="shared" si="1"/>
         <v>7.8025200000000003</v>
       </c>
-      <c r="K10" s="12">
-        <f>C10*D10*G10/1000</f>
-        <v>1.1081400000000001</v>
-      </c>
-      <c r="L10" s="12">
-        <f>C10*D10*H10/1000</f>
-        <v>4.5539999999999997E-2</v>
-      </c>
-      <c r="M10" s="12">
-        <f>C10*D10*I10/1000</f>
+      <c r="L10" s="18">
+        <f t="shared" si="9"/>
+        <v>3.9576428571428575E-2</v>
+      </c>
+      <c r="M10" s="18">
+        <f t="shared" si="10"/>
+        <v>1.7184905660377358E-4</v>
+      </c>
+      <c r="N10" s="12">
+        <f t="shared" si="11"/>
+        <v>8.9562000000000008</v>
+      </c>
+      <c r="O10" s="12">
+        <f t="shared" si="2"/>
         <v>2.7324000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1244,47 +1325,55 @@
         <v>7</v>
       </c>
       <c r="D11" s="12">
-        <f>IF(ISBLANK(A11), "", VLOOKUP($B11, _xlfn.IFS($A11="Cars and light commercial vehicles", $P$36:$W$43,$A11="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A11="Light duty vehicles",$P$49:$W$50,$A11="Heavy duty vehicles",$P$51:$W$58,$A11="Aviation",$P$59:$W$61,$A11="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>3.9300000000000002E-2</v>
       </c>
       <c r="E11" s="12" t="str">
-        <f>IF(ISBLANK(B11), "", VLOOKUP($B11, _xlfn.IFS($A11="Cars and light commercial vehicles", $P$36:$W$43,$A11="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A11="Light duty vehicles",$P$49:$W$50,$A11="Heavy duty vehicles",$P$51:$W$58,$A11="Aviation",$P$59:$W$61,$A11="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/m3</v>
       </c>
       <c r="F11" s="12">
-        <f>IF(ISBLANK(C11), "", VLOOKUP($B11, _xlfn.IFS($A11="Cars and light commercial vehicles", $P$36:$W$43,$A11="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A11="Light duty vehicles",$P$49:$W$50,$A11="Heavy duty vehicles",$P$51:$W$58,$A11="Aviation",$P$59:$W$61,$A11="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>51.4</v>
       </c>
       <c r="G11" s="12">
-        <f>IF(ISBLANK(D11), "", VLOOKUP($B11, _xlfn.IFS($A11="Cars and light commercial vehicles", $P$36:$W$43,$A11="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A11="Light duty vehicles",$P$49:$W$50,$A11="Heavy duty vehicles",$P$51:$W$58,$A11="Aviation",$P$59:$W$61,$A11="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>7.3</v>
       </c>
       <c r="H11" s="12">
-        <f>IF(ISBLANK(E11), "", VLOOKUP($B11, _xlfn.IFS($A11="Cars and light commercial vehicles", $P$36:$W$43,$A11="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A11="Light duty vehicles",$P$49:$W$50,$A11="Heavy duty vehicles",$P$51:$W$58,$A11="Aviation",$P$59:$W$61,$A11="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.3</v>
       </c>
-      <c r="I11" s="12">
-        <f>IF(ISBLANK(F11), "", VLOOKUP($B11, _xlfn.IFS($A11="Cars and light commercial vehicles", $P$36:$W$43,$A11="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A11="Light duty vehicles",$P$49:$W$50,$A11="Heavy duty vehicles",$P$51:$W$58,$A11="Aviation",$P$59:$W$61,$A11="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I11">
+        <f t="shared" si="8"/>
+        <v>59</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="J11" s="12">
-        <f t="shared" ref="J11" si="10">C11*D11*F11/1000</f>
+      <c r="K11" s="12">
+        <f t="shared" si="1"/>
         <v>1.4140140000000001E-2</v>
       </c>
-      <c r="K11" s="12">
-        <f t="shared" ref="K11" si="11">C11*D11*G11/1000</f>
-        <v>2.0082300000000002E-3</v>
-      </c>
-      <c r="L11" s="12">
-        <f t="shared" ref="L11" si="12">C11*D11*H11/1000</f>
-        <v>8.2530000000000011E-5</v>
-      </c>
-      <c r="M11" s="12">
-        <f>C11*D11*I11/1000</f>
+      <c r="L11" s="18">
+        <f t="shared" si="9"/>
+        <v>7.172250000000001E-5</v>
+      </c>
+      <c r="M11" s="18">
+        <f t="shared" si="10"/>
+        <v>3.1143396226415099E-7</v>
+      </c>
+      <c r="N11" s="12">
+        <f t="shared" si="11"/>
+        <v>1.6230900000000003E-2</v>
+      </c>
+      <c r="O11" s="12">
+        <f t="shared" si="2"/>
         <v>4.9518000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1295,47 +1384,55 @@
         <v>8</v>
       </c>
       <c r="D12" s="12">
-        <f>IF(ISBLANK(A12), "", VLOOKUP($B12, _xlfn.IFS($A12="Cars and light commercial vehicles", $P$36:$W$43,$A12="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A12="Light duty vehicles",$P$49:$W$50,$A12="Heavy duty vehicles",$P$51:$W$58,$A12="Aviation",$P$59:$W$61,$A12="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>3.9300000000000002E-2</v>
       </c>
       <c r="E12" s="12" t="str">
-        <f>IF(ISBLANK(B12), "", VLOOKUP($B12, _xlfn.IFS($A12="Cars and light commercial vehicles", $P$36:$W$43,$A12="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A12="Light duty vehicles",$P$49:$W$50,$A12="Heavy duty vehicles",$P$51:$W$58,$A12="Aviation",$P$59:$W$61,$A12="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/m3</v>
       </c>
       <c r="F12" s="12">
-        <f>IF(ISBLANK(C12), "", VLOOKUP($B12, _xlfn.IFS($A12="Cars and light commercial vehicles", $P$36:$W$43,$A12="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A12="Light duty vehicles",$P$49:$W$50,$A12="Heavy duty vehicles",$P$51:$W$58,$A12="Aviation",$P$59:$W$61,$A12="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>51.4</v>
       </c>
       <c r="G12" s="12">
-        <f>IF(ISBLANK(D12), "", VLOOKUP($B12, _xlfn.IFS($A12="Cars and light commercial vehicles", $P$36:$W$43,$A12="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A12="Light duty vehicles",$P$49:$W$50,$A12="Heavy duty vehicles",$P$51:$W$58,$A12="Aviation",$P$59:$W$61,$A12="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>2.8</v>
       </c>
       <c r="H12" s="12">
-        <f>IF(ISBLANK(E12), "", VLOOKUP($B12, _xlfn.IFS($A12="Cars and light commercial vehicles", $P$36:$W$43,$A12="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A12="Light duty vehicles",$P$49:$W$50,$A12="Heavy duty vehicles",$P$51:$W$58,$A12="Aviation",$P$59:$W$61,$A12="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.3</v>
       </c>
-      <c r="I12" s="12">
-        <f>IF(ISBLANK(F12), "", VLOOKUP($B12, _xlfn.IFS($A12="Cars and light commercial vehicles", $P$36:$W$43,$A12="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A12="Light duty vehicles",$P$49:$W$50,$A12="Heavy duty vehicles",$P$51:$W$58,$A12="Aviation",$P$59:$W$61,$A12="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I12">
+        <f t="shared" si="8"/>
+        <v>54.5</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="J12" s="12">
-        <f t="shared" ref="J12" si="13">C12*D12*F12/1000</f>
+      <c r="K12" s="12">
+        <f t="shared" si="1"/>
         <v>1.616016E-2</v>
       </c>
-      <c r="K12" s="12">
-        <f t="shared" ref="K12" si="14">C12*D12*G12/1000</f>
-        <v>8.8031999999999997E-4</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" ref="L12" si="15">C12*D12*H12/1000</f>
-        <v>9.4320000000000005E-5</v>
-      </c>
-      <c r="M12" s="12">
-        <f>C12*D12*I12/1000</f>
+      <c r="L12" s="18">
+        <f t="shared" si="9"/>
+        <v>3.1440000000000004E-5</v>
+      </c>
+      <c r="M12" s="18">
+        <f t="shared" si="10"/>
+        <v>3.5592452830188682E-7</v>
+      </c>
+      <c r="N12" s="12">
+        <f t="shared" si="11"/>
+        <v>1.7134800000000002E-2</v>
+      </c>
+      <c r="O12" s="12">
+        <f t="shared" si="2"/>
         <v>5.6592000000000005E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1346,48 +1443,55 @@
         <v>7</v>
       </c>
       <c r="D13" s="12">
-        <f>IF(ISBLANK(A13), "", VLOOKUP($B13, _xlfn.IFS($A13="Cars and light commercial vehicles", $P$36:$W$43,$A13="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A13="Light duty vehicles",$P$49:$W$50,$A13="Heavy duty vehicles",$P$51:$W$58,$A13="Aviation",$P$59:$W$61,$A13="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>25.3</v>
       </c>
       <c r="E13" s="12" t="str">
-        <f>IF(ISBLANK(B13), "", VLOOKUP($B13, _xlfn.IFS($A13="Cars and light commercial vehicles", $P$36:$W$43,$A13="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A13="Light duty vehicles",$P$49:$W$50,$A13="Heavy duty vehicles",$P$51:$W$58,$A13="Aviation",$P$59:$W$61,$A13="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F13" s="12">
-        <f>IF(ISBLANK(C13), "", VLOOKUP($B13, _xlfn.IFS($A13="Cars and light commercial vehicles", $P$36:$W$43,$A13="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A13="Light duty vehicles",$P$49:$W$50,$A13="Heavy duty vehicles",$P$51:$W$58,$A13="Aviation",$P$59:$W$61,$A13="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>51.4</v>
       </c>
       <c r="G13" s="12">
-        <f>IF(ISBLANK(D13), "", VLOOKUP($B13, _xlfn.IFS($A13="Cars and light commercial vehicles", $P$36:$W$43,$A13="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A13="Light duty vehicles",$P$49:$W$50,$A13="Heavy duty vehicles",$P$51:$W$58,$A13="Aviation",$P$59:$W$61,$A13="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>2.8</v>
       </c>
       <c r="H13" s="12">
-        <f>IF(ISBLANK(E13), "", VLOOKUP($B13, _xlfn.IFS($A13="Cars and light commercial vehicles", $P$36:$W$43,$A13="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A13="Light duty vehicles",$P$49:$W$50,$A13="Heavy duty vehicles",$P$51:$W$58,$A13="Aviation",$P$59:$W$61,$A13="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.3</v>
       </c>
-      <c r="I13" s="12">
-        <f>IF(ISBLANK(F13), "", VLOOKUP($B13, _xlfn.IFS($A13="Cars and light commercial vehicles", $P$36:$W$43,$A13="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A13="Light duty vehicles",$P$49:$W$50,$A13="Heavy duty vehicles",$P$51:$W$58,$A13="Aviation",$P$59:$W$61,$A13="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I13">
+        <f t="shared" si="8"/>
+        <v>54.5</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="J13" s="12">
-        <f>C13*D13*F13/1000</f>
+      <c r="K13" s="12">
+        <f t="shared" si="1"/>
         <v>9.1029399999999985</v>
       </c>
-      <c r="K13" s="12">
-        <f>C13*D13*G13/1000</f>
-        <v>0.49587999999999993</v>
-      </c>
-      <c r="L13" s="12">
-        <f>C13*D13*H13/1000</f>
-        <v>5.3129999999999997E-2</v>
-      </c>
-      <c r="M13" s="12">
-        <f>C13*D13*I13/1000</f>
+      <c r="L13" s="18">
+        <f t="shared" si="9"/>
+        <v>1.7709999999999997E-2</v>
+      </c>
+      <c r="M13" s="18">
+        <f t="shared" si="10"/>
+        <v>2.0049056603773583E-4</v>
+      </c>
+      <c r="N13" s="12">
+        <f t="shared" si="11"/>
+        <v>9.6519499999999994</v>
+      </c>
+      <c r="O13" s="12">
+        <f t="shared" si="2"/>
         <v>3.1877999999999997</v>
       </c>
-      <c r="N13" s="12"/>
-    </row>
-    <row r="14" spans="1:17">
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1398,48 +1502,55 @@
         <v>8</v>
       </c>
       <c r="D14" s="12">
-        <f>IF(ISBLANK(A14), "", VLOOKUP($B14, _xlfn.IFS($A14="Cars and light commercial vehicles", $P$36:$W$43,$A14="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A14="Light duty vehicles",$P$49:$W$50,$A14="Heavy duty vehicles",$P$51:$W$58,$A14="Aviation",$P$59:$W$61,$A14="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>38.6</v>
       </c>
       <c r="E14" s="12" t="str">
-        <f>IF(ISBLANK(B14), "", VLOOKUP($B14, _xlfn.IFS($A14="Cars and light commercial vehicles", $P$36:$W$43,$A14="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A14="Light duty vehicles",$P$49:$W$50,$A14="Heavy duty vehicles",$P$51:$W$58,$A14="Aviation",$P$59:$W$61,$A14="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F14" s="12">
-        <f>IF(ISBLANK(C14), "", VLOOKUP($B14, _xlfn.IFS($A14="Cars and light commercial vehicles", $P$36:$W$43,$A14="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A14="Light duty vehicles",$P$49:$W$50,$A14="Heavy duty vehicles",$P$51:$W$58,$A14="Aviation",$P$59:$W$61,$A14="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G14" s="12">
-        <f>IF(ISBLANK(D14), "", VLOOKUP($B14, _xlfn.IFS($A14="Cars and light commercial vehicles", $P$36:$W$43,$A14="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A14="Light duty vehicles",$P$49:$W$50,$A14="Heavy duty vehicles",$P$51:$W$58,$A14="Aviation",$P$59:$W$61,$A14="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="H14" s="12">
-        <f>IF(ISBLANK(E14), "", VLOOKUP($B14, _xlfn.IFS($A14="Cars and light commercial vehicles", $P$36:$W$43,$A14="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A14="Light duty vehicles",$P$49:$W$50,$A14="Heavy duty vehicles",$P$51:$W$58,$A14="Aviation",$P$59:$W$61,$A14="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.4</v>
       </c>
-      <c r="I14" s="12">
-        <f>IF(ISBLANK(F14), "", VLOOKUP($B14, _xlfn.IFS($A14="Cars and light commercial vehicles", $P$36:$W$43,$A14="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A14="Light duty vehicles",$P$49:$W$50,$A14="Heavy duty vehicles",$P$51:$W$58,$A14="Aviation",$P$59:$W$61,$A14="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I14">
+        <f t="shared" si="8"/>
+        <v>70.37</v>
+      </c>
+      <c r="J14" s="12">
+        <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
-      <c r="J14" s="12">
-        <f>C14*D14*F14/1000</f>
+      <c r="K14" s="12">
+        <f t="shared" si="1"/>
         <v>21.585120000000003</v>
       </c>
-      <c r="K14" s="12">
-        <f>C14*D14*G14/1000</f>
-        <v>2.1616000000000003E-2</v>
-      </c>
-      <c r="L14" s="12">
-        <f>C14*D14*H14/1000</f>
-        <v>0.12352</v>
-      </c>
-      <c r="M14" s="12">
-        <f>C14*D14*I14/1000</f>
+      <c r="L14" s="18">
+        <f t="shared" si="9"/>
+        <v>7.7200000000000012E-4</v>
+      </c>
+      <c r="M14" s="18">
+        <f t="shared" si="10"/>
+        <v>4.6611320754716981E-4</v>
+      </c>
+      <c r="N14" s="12">
+        <f t="shared" si="11"/>
+        <v>21.730256000000001</v>
+      </c>
+      <c r="O14" s="12">
+        <f t="shared" si="2"/>
         <v>5.3422400000000003</v>
       </c>
-      <c r="N14" s="12"/>
-    </row>
-    <row r="15" spans="1:17">
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1450,48 +1561,55 @@
         <v>9</v>
       </c>
       <c r="D15" s="12">
-        <f>IF(ISBLANK(A15), "", VLOOKUP($B15, _xlfn.IFS($A15="Cars and light commercial vehicles", $P$36:$W$43,$A15="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A15="Light duty vehicles",$P$49:$W$50,$A15="Heavy duty vehicles",$P$51:$W$58,$A15="Aviation",$P$59:$W$61,$A15="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>38.6</v>
       </c>
       <c r="E15" s="12" t="str">
-        <f>IF(ISBLANK(B15), "", VLOOKUP($B15, _xlfn.IFS($A15="Cars and light commercial vehicles", $P$36:$W$43,$A15="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A15="Light duty vehicles",$P$49:$W$50,$A15="Heavy duty vehicles",$P$51:$W$58,$A15="Aviation",$P$59:$W$61,$A15="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F15" s="12">
-        <f>IF(ISBLANK(C15), "", VLOOKUP($B15, _xlfn.IFS($A15="Cars and light commercial vehicles", $P$36:$W$43,$A15="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A15="Light duty vehicles",$P$49:$W$50,$A15="Heavy duty vehicles",$P$51:$W$58,$A15="Aviation",$P$59:$W$61,$A15="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G15" s="12">
-        <f>IF(ISBLANK(D15), "", VLOOKUP($B15, _xlfn.IFS($A15="Cars and light commercial vehicles", $P$36:$W$43,$A15="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A15="Light duty vehicles",$P$49:$W$50,$A15="Heavy duty vehicles",$P$51:$W$58,$A15="Aviation",$P$59:$W$61,$A15="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>0.1</v>
       </c>
       <c r="H15" s="12">
-        <f>IF(ISBLANK(E15), "", VLOOKUP($B15, _xlfn.IFS($A15="Cars and light commercial vehicles", $P$36:$W$43,$A15="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A15="Light duty vehicles",$P$49:$W$50,$A15="Heavy duty vehicles",$P$51:$W$58,$A15="Aviation",$P$59:$W$61,$A15="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.4</v>
       </c>
-      <c r="I15" s="12">
-        <f>IF(ISBLANK(F15), "", VLOOKUP($B15, _xlfn.IFS($A15="Cars and light commercial vehicles", $P$36:$W$43,$A15="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A15="Light duty vehicles",$P$49:$W$50,$A15="Heavy duty vehicles",$P$51:$W$58,$A15="Aviation",$P$59:$W$61,$A15="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I15">
+        <f t="shared" si="8"/>
+        <v>70.400000000000006</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
-      <c r="J15" s="12">
-        <f>C15*D15*F15/1000</f>
+      <c r="K15" s="12">
+        <f t="shared" si="1"/>
         <v>24.283260000000006</v>
       </c>
-      <c r="K15" s="12">
-        <f>C15*D15*G15/1000</f>
-        <v>3.474E-2</v>
-      </c>
-      <c r="L15" s="12">
-        <f>C15*D15*H15/1000</f>
-        <v>0.13896</v>
-      </c>
-      <c r="M15" s="12">
-        <f>C15*D15*I15/1000</f>
+      <c r="L15" s="18">
+        <f t="shared" si="9"/>
+        <v>1.240714285714286E-3</v>
+      </c>
+      <c r="M15" s="18">
+        <f t="shared" si="10"/>
+        <v>5.2437735849056614E-4</v>
+      </c>
+      <c r="N15" s="12">
+        <f t="shared" si="11"/>
+        <v>24.456960000000002</v>
+      </c>
+      <c r="O15" s="12">
+        <f t="shared" si="2"/>
         <v>6.0100200000000008</v>
       </c>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:17">
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1502,46 +1620,53 @@
         <v>10</v>
       </c>
       <c r="D16" s="12">
-        <f>IF(ISBLANK(A16), "", VLOOKUP($B16, _xlfn.IFS($A16="Cars and light commercial vehicles", $P$36:$W$43,$A16="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A16="Light duty vehicles",$P$49:$W$50,$A16="Heavy duty vehicles",$P$51:$W$58,$A16="Aviation",$P$59:$W$61,$A16="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>38.6</v>
       </c>
       <c r="E16" s="12" t="str">
-        <f>IF(ISBLANK(B16), "", VLOOKUP($B16, _xlfn.IFS($A16="Cars and light commercial vehicles", $P$36:$W$43,$A16="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A16="Light duty vehicles",$P$49:$W$50,$A16="Heavy duty vehicles",$P$51:$W$58,$A16="Aviation",$P$59:$W$61,$A16="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F16" s="12">
-        <f>IF(ISBLANK(C16), "", VLOOKUP($B16, _xlfn.IFS($A16="Cars and light commercial vehicles", $P$36:$W$43,$A16="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A16="Light duty vehicles",$P$49:$W$50,$A16="Heavy duty vehicles",$P$51:$W$58,$A16="Aviation",$P$59:$W$61,$A16="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G16" s="12">
-        <f>IF(ISBLANK(D16), "", VLOOKUP($B16, _xlfn.IFS($A16="Cars and light commercial vehicles", $P$36:$W$43,$A16="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A16="Light duty vehicles",$P$49:$W$50,$A16="Heavy duty vehicles",$P$51:$W$58,$A16="Aviation",$P$59:$W$61,$A16="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
       <c r="H16" s="12">
-        <f>IF(ISBLANK(E16), "", VLOOKUP($B16, _xlfn.IFS($A16="Cars and light commercial vehicles", $P$36:$W$43,$A16="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A16="Light duty vehicles",$P$49:$W$50,$A16="Heavy duty vehicles",$P$51:$W$58,$A16="Aviation",$P$59:$W$61,$A16="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.4</v>
       </c>
-      <c r="I16" s="12">
-        <f>IF(ISBLANK(F16), "", VLOOKUP($B16, _xlfn.IFS($A16="Cars and light commercial vehicles", $P$36:$W$43,$A16="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A16="Light duty vehicles",$P$49:$W$50,$A16="Heavy duty vehicles",$P$51:$W$58,$A16="Aviation",$P$59:$W$61,$A16="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I16">
+        <f t="shared" si="8"/>
+        <v>70.5</v>
+      </c>
+      <c r="J16" s="12">
+        <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
-      <c r="J16" s="12">
-        <f>C16*D16*F16/1000</f>
+      <c r="K16" s="12">
+        <f t="shared" si="1"/>
         <v>26.981400000000001</v>
       </c>
-      <c r="K16" s="12">
-        <f>C16*D16*G16/1000</f>
-        <v>7.7200000000000005E-2</v>
-      </c>
-      <c r="L16" s="12">
-        <f>C16*D16*H16/1000</f>
-        <v>0.15440000000000001</v>
-      </c>
-      <c r="M16" s="12">
-        <f>C16*D16*I16/1000</f>
+      <c r="L16" s="18">
+        <f t="shared" si="9"/>
+        <v>2.7571428571428573E-3</v>
+      </c>
+      <c r="M16" s="18">
+        <f t="shared" si="10"/>
+        <v>5.8264150943396231E-4</v>
+      </c>
+      <c r="N16" s="12">
+        <f t="shared" si="11"/>
+        <v>27.213000000000001</v>
+      </c>
+      <c r="O16" s="12">
+        <f t="shared" si="2"/>
         <v>6.6778000000000004</v>
       </c>
-      <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
@@ -1554,46 +1679,53 @@
         <v>8</v>
       </c>
       <c r="D17" s="12">
-        <f>IF(ISBLANK(A17), "", VLOOKUP($B17, _xlfn.IFS($A17="Cars and light commercial vehicles", $P$36:$W$43,$A17="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A17="Light duty vehicles",$P$49:$W$50,$A17="Heavy duty vehicles",$P$51:$W$58,$A17="Aviation",$P$59:$W$61,$A17="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>33.1</v>
       </c>
       <c r="E17" s="12" t="str">
-        <f>IF(ISBLANK(B17), "", VLOOKUP($B17, _xlfn.IFS($A17="Cars and light commercial vehicles", $P$36:$W$43,$A17="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A17="Light duty vehicles",$P$49:$W$50,$A17="Heavy duty vehicles",$P$51:$W$58,$A17="Aviation",$P$59:$W$61,$A17="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F17" s="12">
-        <f>IF(ISBLANK(C17), "", VLOOKUP($B17, _xlfn.IFS($A17="Cars and light commercial vehicles", $P$36:$W$43,$A17="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A17="Light duty vehicles",$P$49:$W$50,$A17="Heavy duty vehicles",$P$51:$W$58,$A17="Aviation",$P$59:$W$61,$A17="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>67</v>
       </c>
       <c r="G17" s="12">
-        <f>IF(ISBLANK(D17), "", VLOOKUP($B17, _xlfn.IFS($A17="Cars and light commercial vehicles", $P$36:$W$43,$A17="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A17="Light duty vehicles",$P$49:$W$50,$A17="Heavy duty vehicles",$P$51:$W$58,$A17="Aviation",$P$59:$W$61,$A17="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>0.06</v>
       </c>
       <c r="H17" s="12">
-        <f>IF(ISBLANK(E17), "", VLOOKUP($B17, _xlfn.IFS($A17="Cars and light commercial vehicles", $P$36:$W$43,$A17="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A17="Light duty vehicles",$P$49:$W$50,$A17="Heavy duty vehicles",$P$51:$W$58,$A17="Aviation",$P$59:$W$61,$A17="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
-      <c r="I17" s="12">
-        <f>IF(ISBLANK(F17), "", VLOOKUP($B17, _xlfn.IFS($A17="Cars and light commercial vehicles", $P$36:$W$43,$A17="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A17="Light duty vehicles",$P$49:$W$50,$A17="Heavy duty vehicles",$P$51:$W$58,$A17="Aviation",$P$59:$W$61,$A17="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I17">
+        <f t="shared" si="8"/>
+        <v>67.66</v>
+      </c>
+      <c r="J17" s="12">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="J17" s="12">
-        <f>C17*D17*F17/1000</f>
+      <c r="K17" s="12">
+        <f t="shared" si="1"/>
         <v>17.741600000000002</v>
       </c>
-      <c r="K17" s="12">
-        <f>C17*D17*G17/1000</f>
-        <v>1.5887999999999999E-2</v>
-      </c>
-      <c r="L17" s="12">
-        <f>C17*D17*H17/1000</f>
-        <v>0.15887999999999999</v>
-      </c>
-      <c r="M17" s="12">
-        <f>C17*D17*I17/1000</f>
+      <c r="L17" s="18">
+        <f t="shared" si="9"/>
+        <v>5.6742857142857137E-4</v>
+      </c>
+      <c r="M17" s="18">
+        <f t="shared" si="10"/>
+        <v>5.9954716981132068E-4</v>
+      </c>
+      <c r="N17" s="12">
+        <f t="shared" si="11"/>
+        <v>17.916367999999999</v>
+      </c>
+      <c r="O17" s="12">
+        <f t="shared" si="2"/>
         <v>4.7664000000000009</v>
       </c>
-      <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
@@ -1606,46 +1738,53 @@
         <v>9</v>
       </c>
       <c r="D18" s="12">
-        <f>IF(ISBLANK(A18), "", VLOOKUP($B18, _xlfn.IFS($A18="Cars and light commercial vehicles", $P$36:$W$43,$A18="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A18="Light duty vehicles",$P$49:$W$50,$A18="Heavy duty vehicles",$P$51:$W$58,$A18="Aviation",$P$59:$W$61,$A18="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>36.799999999999997</v>
       </c>
       <c r="E18" s="12" t="str">
-        <f>IF(ISBLANK(B18), "", VLOOKUP($B18, _xlfn.IFS($A18="Cars and light commercial vehicles", $P$36:$W$43,$A18="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A18="Light duty vehicles",$P$49:$W$50,$A18="Heavy duty vehicles",$P$51:$W$58,$A18="Aviation",$P$59:$W$61,$A18="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F18" s="12">
-        <f>IF(ISBLANK(C18), "", VLOOKUP($B18, _xlfn.IFS($A18="Cars and light commercial vehicles", $P$36:$W$43,$A18="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A18="Light duty vehicles",$P$49:$W$50,$A18="Heavy duty vehicles",$P$51:$W$58,$A18="Aviation",$P$59:$W$61,$A18="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>69.599999999999994</v>
       </c>
       <c r="G18" s="12">
-        <f>IF(ISBLANK(D18), "", VLOOKUP($B18, _xlfn.IFS($A18="Cars and light commercial vehicles", $P$36:$W$43,$A18="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A18="Light duty vehicles",$P$49:$W$50,$A18="Heavy duty vehicles",$P$51:$W$58,$A18="Aviation",$P$59:$W$61,$A18="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>0.01</v>
       </c>
       <c r="H18" s="12">
-        <f>IF(ISBLANK(E18), "", VLOOKUP($B18, _xlfn.IFS($A18="Cars and light commercial vehicles", $P$36:$W$43,$A18="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A18="Light duty vehicles",$P$49:$W$50,$A18="Heavy duty vehicles",$P$51:$W$58,$A18="Aviation",$P$59:$W$61,$A18="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
-      <c r="I18" s="12">
-        <f>IF(ISBLANK(F18), "", VLOOKUP($B18, _xlfn.IFS($A18="Cars and light commercial vehicles", $P$36:$W$43,$A18="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A18="Light duty vehicles",$P$49:$W$50,$A18="Heavy duty vehicles",$P$51:$W$58,$A18="Aviation",$P$59:$W$61,$A18="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I18">
+        <f t="shared" si="8"/>
+        <v>70.209999999999994</v>
+      </c>
+      <c r="J18" s="12">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="J18" s="12">
-        <f>C18*D18*F18/1000</f>
+      <c r="K18" s="12">
+        <f t="shared" si="1"/>
         <v>23.051519999999996</v>
       </c>
-      <c r="K18" s="12">
-        <f>C18*D18*G18/1000</f>
-        <v>3.3119999999999998E-3</v>
-      </c>
-      <c r="L18" s="12">
-        <f>C18*D18*H18/1000</f>
-        <v>0.19872000000000001</v>
-      </c>
-      <c r="M18" s="12">
-        <f>C18*D18*I18/1000</f>
+      <c r="L18" s="18">
+        <f t="shared" si="9"/>
+        <v>1.1828571428571429E-4</v>
+      </c>
+      <c r="M18" s="18">
+        <f t="shared" si="10"/>
+        <v>7.498867924528302E-4</v>
+      </c>
+      <c r="N18" s="12">
+        <f t="shared" si="11"/>
+        <v>23.253551999999996</v>
+      </c>
+      <c r="O18" s="12">
+        <f t="shared" si="2"/>
         <v>5.9615999999999998</v>
       </c>
-      <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
@@ -1658,46 +1797,53 @@
         <v>9</v>
       </c>
       <c r="D19" s="12">
-        <f>IF(ISBLANK(A19), "", VLOOKUP($B19, _xlfn.IFS($A19="Cars and light commercial vehicles", $P$36:$W$43,$A19="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A19="Light duty vehicles",$P$49:$W$50,$A19="Heavy duty vehicles",$P$51:$W$58,$A19="Aviation",$P$59:$W$61,$A19="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>34.200000000000003</v>
       </c>
       <c r="E19" s="12" t="str">
-        <f>IF(ISBLANK(B19), "", VLOOKUP($B19, _xlfn.IFS($A19="Cars and light commercial vehicles", $P$36:$W$43,$A19="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A19="Light duty vehicles",$P$49:$W$50,$A19="Heavy duty vehicles",$P$51:$W$58,$A19="Aviation",$P$59:$W$61,$A19="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F19" s="12">
-        <f>IF(ISBLANK(C19), "", VLOOKUP($B19, _xlfn.IFS($A19="Cars and light commercial vehicles", $P$36:$W$43,$A19="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A19="Light duty vehicles",$P$49:$W$50,$A19="Heavy duty vehicles",$P$51:$W$58,$A19="Aviation",$P$59:$W$61,$A19="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>67.400000000000006</v>
       </c>
       <c r="G19" s="12">
-        <f>IF(ISBLANK(D19), "", VLOOKUP($B19, _xlfn.IFS($A19="Cars and light commercial vehicles", $P$36:$W$43,$A19="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A19="Light duty vehicles",$P$49:$W$50,$A19="Heavy duty vehicles",$P$51:$W$58,$A19="Aviation",$P$59:$W$61,$A19="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>10.1</v>
       </c>
       <c r="H19" s="12">
-        <f>IF(ISBLANK(E19), "", VLOOKUP($B19, _xlfn.IFS($A19="Cars and light commercial vehicles", $P$36:$W$43,$A19="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A19="Light duty vehicles",$P$49:$W$50,$A19="Heavy duty vehicles",$P$51:$W$58,$A19="Aviation",$P$59:$W$61,$A19="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.3</v>
       </c>
-      <c r="I19" s="12">
-        <f>IF(ISBLANK(F19), "", VLOOKUP($B19, _xlfn.IFS($A19="Cars and light commercial vehicles", $P$36:$W$43,$A19="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A19="Light duty vehicles",$P$49:$W$50,$A19="Heavy duty vehicles",$P$51:$W$58,$A19="Aviation",$P$59:$W$61,$A19="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I19">
+        <f t="shared" si="8"/>
+        <v>77.8</v>
+      </c>
+      <c r="J19" s="12">
+        <f t="shared" si="0"/>
         <v>17.2</v>
       </c>
-      <c r="J19" s="12">
-        <f>C19*D19*F19/1000</f>
+      <c r="K19" s="12">
+        <f t="shared" si="1"/>
         <v>20.745720000000002</v>
       </c>
-      <c r="K19" s="12">
-        <f>C19*D19*G19/1000</f>
-        <v>3.1087800000000003</v>
-      </c>
-      <c r="L19" s="12">
-        <f>C19*D19*H19/1000</f>
-        <v>9.2340000000000005E-2</v>
-      </c>
-      <c r="M19" s="12">
-        <f>C19*D19*I19/1000</f>
+      <c r="L19" s="18">
+        <f t="shared" si="9"/>
+        <v>0.11102785714285715</v>
+      </c>
+      <c r="M19" s="18">
+        <f t="shared" si="10"/>
+        <v>3.4845283018867927E-4</v>
+      </c>
+      <c r="N19" s="12">
+        <f t="shared" si="11"/>
+        <v>23.946840000000002</v>
+      </c>
+      <c r="O19" s="12">
+        <f t="shared" si="2"/>
         <v>5.2941599999999998</v>
       </c>
-      <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
@@ -1710,46 +1856,53 @@
         <v>10</v>
       </c>
       <c r="D20" s="12">
-        <f>IF(ISBLANK(A20), "", VLOOKUP($B20, _xlfn.IFS($A20="Cars and light commercial vehicles", $P$36:$W$43,$A20="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A20="Light duty vehicles",$P$49:$W$50,$A20="Heavy duty vehicles",$P$51:$W$58,$A20="Aviation",$P$59:$W$61,$A20="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>38.6</v>
       </c>
       <c r="E20" s="12" t="str">
-        <f>IF(ISBLANK(B20), "", VLOOKUP($B20, _xlfn.IFS($A20="Cars and light commercial vehicles", $P$36:$W$43,$A20="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A20="Light duty vehicles",$P$49:$W$50,$A20="Heavy duty vehicles",$P$51:$W$58,$A20="Aviation",$P$59:$W$61,$A20="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F20" s="12">
-        <f>IF(ISBLANK(C20), "", VLOOKUP($B20, _xlfn.IFS($A20="Cars and light commercial vehicles", $P$36:$W$43,$A20="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A20="Light duty vehicles",$P$49:$W$50,$A20="Heavy duty vehicles",$P$51:$W$58,$A20="Aviation",$P$59:$W$61,$A20="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G20" s="12">
-        <f>IF(ISBLANK(D20), "", VLOOKUP($B20, _xlfn.IFS($A20="Cars and light commercial vehicles", $P$36:$W$43,$A20="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A20="Light duty vehicles",$P$49:$W$50,$A20="Heavy duty vehicles",$P$51:$W$58,$A20="Aviation",$P$59:$W$61,$A20="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
       <c r="H20" s="12">
-        <f>IF(ISBLANK(E20), "", VLOOKUP($B20, _xlfn.IFS($A20="Cars and light commercial vehicles", $P$36:$W$43,$A20="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A20="Light duty vehicles",$P$49:$W$50,$A20="Heavy duty vehicles",$P$51:$W$58,$A20="Aviation",$P$59:$W$61,$A20="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
-      <c r="I20" s="12">
-        <f>IF(ISBLANK(F20), "", VLOOKUP($B20, _xlfn.IFS($A20="Cars and light commercial vehicles", $P$36:$W$43,$A20="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A20="Light duty vehicles",$P$49:$W$50,$A20="Heavy duty vehicles",$P$51:$W$58,$A20="Aviation",$P$59:$W$61,$A20="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I20">
+        <f t="shared" si="8"/>
+        <v>70.600000000000009</v>
+      </c>
+      <c r="J20" s="12">
+        <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
-      <c r="J20" s="12">
-        <f t="shared" ref="J20:J21" si="16">C20*D20*F20/1000</f>
+      <c r="K20" s="12">
+        <f t="shared" si="1"/>
         <v>26.981400000000001</v>
       </c>
-      <c r="K20" s="12">
-        <f t="shared" ref="K20:K21" si="17">C20*D20*G20/1000</f>
-        <v>7.7200000000000005E-2</v>
-      </c>
-      <c r="L20" s="12">
-        <f t="shared" ref="L20:L21" si="18">C20*D20*H20/1000</f>
-        <v>0.193</v>
-      </c>
-      <c r="M20" s="12">
-        <f>C20*D20*I20/1000</f>
+      <c r="L20" s="18">
+        <f t="shared" si="9"/>
+        <v>2.7571428571428573E-3</v>
+      </c>
+      <c r="M20" s="18">
+        <f t="shared" si="10"/>
+        <v>7.2830188679245283E-4</v>
+      </c>
+      <c r="N20" s="12">
+        <f t="shared" si="11"/>
+        <v>27.251600000000003</v>
+      </c>
+      <c r="O20" s="12">
+        <f t="shared" si="2"/>
         <v>6.6778000000000004</v>
       </c>
-      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" t="s">
@@ -1762,43 +1915,51 @@
         <v>11</v>
       </c>
       <c r="D21" s="12">
-        <f>IF(ISBLANK(A21), "", VLOOKUP($B21, _xlfn.IFS($A21="Cars and light commercial vehicles", $P$36:$W$43,$A21="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A21="Light duty vehicles",$P$49:$W$50,$A21="Heavy duty vehicles",$P$51:$W$58,$A21="Aviation",$P$59:$W$61,$A21="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>39.700000000000003</v>
       </c>
       <c r="E21" s="12" t="str">
-        <f>IF(ISBLANK(B21), "", VLOOKUP($B21, _xlfn.IFS($A21="Cars and light commercial vehicles", $P$36:$W$43,$A21="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A21="Light duty vehicles",$P$49:$W$50,$A21="Heavy duty vehicles",$P$51:$W$58,$A21="Aviation",$P$59:$W$61,$A21="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F21" s="12">
-        <f>IF(ISBLANK(C21), "", VLOOKUP($B21, _xlfn.IFS($A21="Cars and light commercial vehicles", $P$36:$W$43,$A21="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A21="Light duty vehicles",$P$49:$W$50,$A21="Heavy duty vehicles",$P$51:$W$58,$A21="Aviation",$P$59:$W$61,$A21="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>73.599999999999994</v>
       </c>
       <c r="G21" s="12">
-        <f>IF(ISBLANK(D21), "", VLOOKUP($B21, _xlfn.IFS($A21="Cars and light commercial vehicles", $P$36:$W$43,$A21="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A21="Light duty vehicles",$P$49:$W$50,$A21="Heavy duty vehicles",$P$51:$W$58,$A21="Aviation",$P$59:$W$61,$A21="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
       <c r="H21" s="12">
-        <f>IF(ISBLANK(E21), "", VLOOKUP($B21, _xlfn.IFS($A21="Cars and light commercial vehicles", $P$36:$W$43,$A21="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A21="Light duty vehicles",$P$49:$W$50,$A21="Heavy duty vehicles",$P$51:$W$58,$A21="Aviation",$P$59:$W$61,$A21="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
-      <c r="I21" s="12">
-        <f>IF(ISBLANK(F21), "", VLOOKUP($B21, _xlfn.IFS($A21="Cars and light commercial vehicles", $P$36:$W$43,$A21="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A21="Light duty vehicles",$P$49:$W$50,$A21="Heavy duty vehicles",$P$51:$W$58,$A21="Aviation",$P$59:$W$61,$A21="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I21">
+        <f t="shared" si="8"/>
+        <v>74.3</v>
+      </c>
+      <c r="J21" s="12">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="J21" s="12">
-        <f t="shared" si="16"/>
+      <c r="K21" s="12">
+        <f t="shared" si="1"/>
         <v>32.141120000000001</v>
       </c>
-      <c r="K21" s="12">
-        <f t="shared" si="17"/>
-        <v>8.7340000000000015E-2</v>
-      </c>
-      <c r="L21" s="12">
-        <f t="shared" si="18"/>
-        <v>0.21835000000000002</v>
-      </c>
-      <c r="M21" s="12">
-        <f>C21*D21*I21/1000</f>
+      <c r="L21" s="18">
+        <f t="shared" si="9"/>
+        <v>3.1192857142857151E-3</v>
+      </c>
+      <c r="M21" s="18">
+        <f t="shared" si="10"/>
+        <v>8.2396226415094355E-4</v>
+      </c>
+      <c r="N21" s="12">
+        <f t="shared" si="11"/>
+        <v>32.446809999999999</v>
+      </c>
+      <c r="O21" s="12">
+        <f t="shared" si="2"/>
         <v>7.8606000000000007</v>
       </c>
     </row>
@@ -1813,43 +1974,51 @@
         <v>10</v>
       </c>
       <c r="D22" s="12">
-        <f>IF(ISBLANK(A22), "", VLOOKUP($B22, _xlfn.IFS($A22="Cars and light commercial vehicles", $P$36:$W$43,$A22="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A22="Light duty vehicles",$P$49:$W$50,$A22="Heavy duty vehicles",$P$51:$W$58,$A22="Aviation",$P$59:$W$61,$A22="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="12"/>
         <v>38.6</v>
       </c>
       <c r="E22" s="12" t="str">
-        <f>IF(ISBLANK(B22), "", VLOOKUP($B22, _xlfn.IFS($A22="Cars and light commercial vehicles", $P$36:$W$43,$A22="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A22="Light duty vehicles",$P$49:$W$50,$A22="Heavy duty vehicles",$P$51:$W$58,$A22="Aviation",$P$59:$W$61,$A22="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="13"/>
         <v>GJ/kL</v>
       </c>
       <c r="F22" s="12">
-        <f>IF(ISBLANK(C22), "", VLOOKUP($B22, _xlfn.IFS($A22="Cars and light commercial vehicles", $P$36:$W$43,$A22="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A22="Light duty vehicles",$P$49:$W$50,$A22="Heavy duty vehicles",$P$51:$W$58,$A22="Aviation",$P$59:$W$61,$A22="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G22" s="12">
-        <f>IF(ISBLANK(D22), "", VLOOKUP($B22, _xlfn.IFS($A22="Cars and light commercial vehicles", $P$36:$W$43,$A22="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A22="Light duty vehicles",$P$49:$W$50,$A22="Heavy duty vehicles",$P$51:$W$58,$A22="Aviation",$P$59:$W$61,$A22="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="15"/>
         <v>0.3</v>
       </c>
       <c r="H22" s="12">
-        <f>IF(ISBLANK(E22), "", VLOOKUP($B22, _xlfn.IFS($A22="Cars and light commercial vehicles", $P$36:$W$43,$A22="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A22="Light duty vehicles",$P$49:$W$50,$A22="Heavy duty vehicles",$P$51:$W$58,$A22="Aviation",$P$59:$W$61,$A22="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
-      <c r="I22" s="12">
-        <f>IF(ISBLANK(F22), "", VLOOKUP($B22, _xlfn.IFS($A22="Cars and light commercial vehicles", $P$36:$W$43,$A22="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A22="Light duty vehicles",$P$49:$W$50,$A22="Heavy duty vehicles",$P$51:$W$58,$A22="Aviation",$P$59:$W$61,$A22="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+      <c r="I22">
+        <f t="shared" si="8"/>
+        <v>70.7</v>
+      </c>
+      <c r="J22" s="12">
+        <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
-      <c r="J22" s="12">
-        <f>C22*D22*F22/1000</f>
+      <c r="K22" s="12">
+        <f t="shared" si="1"/>
         <v>26.981400000000001</v>
       </c>
-      <c r="K22" s="12">
-        <f>C22*D22*G22/1000</f>
-        <v>0.1158</v>
-      </c>
-      <c r="L22" s="12">
-        <f>C22*D22*H22/1000</f>
-        <v>0.193</v>
-      </c>
-      <c r="M22" s="12">
-        <f>C22*D22*I22/1000</f>
+      <c r="L22" s="18">
+        <f t="shared" si="9"/>
+        <v>4.1357142857142851E-3</v>
+      </c>
+      <c r="M22" s="18">
+        <f t="shared" si="10"/>
+        <v>7.2830188679245283E-4</v>
+      </c>
+      <c r="N22" s="12">
+        <f t="shared" si="11"/>
+        <v>27.290200000000002</v>
+      </c>
+      <c r="O22" s="12">
+        <f t="shared" si="2"/>
         <v>6.6778000000000004</v>
       </c>
     </row>
@@ -1885,7 +2054,7 @@
     </row>
     <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
@@ -1912,43 +2081,43 @@
         <v>9</v>
       </c>
       <c r="D32" s="12">
-        <f>IF(ISBLANK(A32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" ref="D32:D39" si="17">IF(ISBLANK(A32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
         <v>23.4</v>
       </c>
       <c r="E32" s="12" t="str">
-        <f>IF(ISBLANK(B32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" ref="E32:E39" si="18">IF(ISBLANK(B32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
         <v>GJ/kL</v>
       </c>
       <c r="F32" s="12">
-        <f>IF(ISBLANK(C32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" ref="F32:F39" si="19">IF(ISBLANK(C32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
         <v>0</v>
       </c>
       <c r="G32" s="12">
-        <f>IF(ISBLANK(D32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" ref="G32:G39" si="20">IF(ISBLANK(D32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
         <v>0.2</v>
       </c>
       <c r="H32" s="12">
-        <f>IF(ISBLANK(E32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" ref="H32:H39" si="21">IF(ISBLANK(E32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
         <v>0.2</v>
       </c>
       <c r="I32" s="12" t="str">
-        <f>IF(ISBLANK(F32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" ref="I32:I39" si="22">IF(ISBLANK(F32), "", VLOOKUP($B32, _xlfn.IFS($A32="Cars and light commercial vehicles", $P$36:$W$43,$A32="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A32="Light duty vehicles",$P$49:$W$50,$A32="Heavy duty vehicles",$P$51:$W$58,$A32="Aviation",$P$59:$W$61,$A32="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
         <v>NE</v>
       </c>
       <c r="J32" s="12">
-        <f>C32*D32*F32/1000</f>
+        <f t="shared" ref="J32:J39" si="23">C32*D32*F32/1000</f>
         <v>0</v>
       </c>
       <c r="K32" s="12">
-        <f>C32*D32*G32/1000</f>
+        <f t="shared" ref="K32:K39" si="24">C32*D32*G32/1000</f>
         <v>4.2120000000000005E-2</v>
       </c>
       <c r="L32" s="12">
-        <f>C32*D32*H32/1000</f>
+        <f t="shared" ref="L32:L39" si="25">C32*D32*H32/1000</f>
         <v>4.2120000000000005E-2</v>
       </c>
       <c r="M32" s="12" t="e">
-        <f>C32*D32*I32/1000</f>
+        <f t="shared" ref="M32:M39" si="26">C32*D32*I32/1000</f>
         <v>#VALUE!</v>
       </c>
       <c r="N32" s="12"/>
@@ -1966,43 +2135,43 @@
         <v>10</v>
       </c>
       <c r="D33" s="12">
-        <f>IF(ISBLANK(A33), "", VLOOKUP($B33, _xlfn.IFS($A33="Cars and light commercial vehicles", $P$36:$W$43,$A33="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A33="Light duty vehicles",$P$49:$W$50,$A33="Heavy duty vehicles",$P$51:$W$58,$A33="Aviation",$P$59:$W$61,$A33="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="17"/>
         <v>34.6</v>
       </c>
       <c r="E33" s="12" t="str">
-        <f>IF(ISBLANK(B33), "", VLOOKUP($B33, _xlfn.IFS($A33="Cars and light commercial vehicles", $P$36:$W$43,$A33="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A33="Light duty vehicles",$P$49:$W$50,$A33="Heavy duty vehicles",$P$51:$W$58,$A33="Aviation",$P$59:$W$61,$A33="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="18"/>
         <v>GJ/kL</v>
       </c>
       <c r="F33" s="12">
-        <f>IF(ISBLANK(C33), "", VLOOKUP($B33, _xlfn.IFS($A33="Cars and light commercial vehicles", $P$36:$W$43,$A33="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A33="Light duty vehicles",$P$49:$W$50,$A33="Heavy duty vehicles",$P$51:$W$58,$A33="Aviation",$P$59:$W$61,$A33="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G33" s="12">
-        <f>IF(ISBLANK(D33), "", VLOOKUP($B33, _xlfn.IFS($A33="Cars and light commercial vehicles", $P$36:$W$43,$A33="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A33="Light duty vehicles",$P$49:$W$50,$A33="Heavy duty vehicles",$P$51:$W$58,$A33="Aviation",$P$59:$W$61,$A33="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="20"/>
         <v>0.8</v>
       </c>
       <c r="H33" s="12">
-        <f>IF(ISBLANK(E33), "", VLOOKUP($B33, _xlfn.IFS($A33="Cars and light commercial vehicles", $P$36:$W$43,$A33="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A33="Light duty vehicles",$P$49:$W$50,$A33="Heavy duty vehicles",$P$51:$W$58,$A33="Aviation",$P$59:$W$61,$A33="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="21"/>
         <v>1.7</v>
       </c>
       <c r="I33" s="12" t="str">
-        <f>IF(ISBLANK(F33), "", VLOOKUP($B33, _xlfn.IFS($A33="Cars and light commercial vehicles", $P$36:$W$43,$A33="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A33="Light duty vehicles",$P$49:$W$50,$A33="Heavy duty vehicles",$P$51:$W$58,$A33="Aviation",$P$59:$W$61,$A33="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" si="22"/>
         <v>NE</v>
       </c>
       <c r="J33" s="12">
-        <f>C33*D33*F33/1000</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K33" s="12">
-        <f>C33*D33*G33/1000</f>
+        <f t="shared" si="24"/>
         <v>0.27679999999999999</v>
       </c>
       <c r="L33" s="12">
-        <f>C33*D33*H33/1000</f>
+        <f t="shared" si="25"/>
         <v>0.58819999999999995</v>
       </c>
       <c r="M33" s="12" t="e">
-        <f>C33*D33*I33/1000</f>
+        <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
       <c r="N33" s="12"/>
@@ -2018,43 +2187,43 @@
         <v>11</v>
       </c>
       <c r="D34" s="12">
-        <f>IF(ISBLANK(A34), "", VLOOKUP($B34, _xlfn.IFS($A34="Cars and light commercial vehicles", $P$36:$W$43,$A34="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A34="Light duty vehicles",$P$49:$W$50,$A34="Heavy duty vehicles",$P$51:$W$58,$A34="Aviation",$P$59:$W$61,$A34="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="17"/>
         <v>38.6</v>
       </c>
       <c r="E34" s="12" t="str">
-        <f>IF(ISBLANK(B34), "", VLOOKUP($B34, _xlfn.IFS($A34="Cars and light commercial vehicles", $P$36:$W$43,$A34="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A34="Light duty vehicles",$P$49:$W$50,$A34="Heavy duty vehicles",$P$51:$W$58,$A34="Aviation",$P$59:$W$61,$A34="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="18"/>
         <v>GJ/kL</v>
       </c>
       <c r="F34" s="12">
-        <f>IF(ISBLANK(C34), "", VLOOKUP($B34, _xlfn.IFS($A34="Cars and light commercial vehicles", $P$36:$W$43,$A34="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A34="Light duty vehicles",$P$49:$W$50,$A34="Heavy duty vehicles",$P$51:$W$58,$A34="Aviation",$P$59:$W$61,$A34="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G34" s="12">
-        <f>IF(ISBLANK(D34), "", VLOOKUP($B34, _xlfn.IFS($A34="Cars and light commercial vehicles", $P$36:$W$43,$A34="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A34="Light duty vehicles",$P$49:$W$50,$A34="Heavy duty vehicles",$P$51:$W$58,$A34="Aviation",$P$59:$W$61,$A34="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="20"/>
         <v>0.01</v>
       </c>
       <c r="H34" s="12">
-        <f>IF(ISBLANK(E34), "", VLOOKUP($B34, _xlfn.IFS($A34="Cars and light commercial vehicles", $P$36:$W$43,$A34="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A34="Light duty vehicles",$P$49:$W$50,$A34="Heavy duty vehicles",$P$51:$W$58,$A34="Aviation",$P$59:$W$61,$A34="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="21"/>
         <v>0.5</v>
       </c>
       <c r="I34" s="12" t="str">
-        <f>IF(ISBLANK(F34), "", VLOOKUP($B34, _xlfn.IFS($A34="Cars and light commercial vehicles", $P$36:$W$43,$A34="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A34="Light duty vehicles",$P$49:$W$50,$A34="Heavy duty vehicles",$P$51:$W$58,$A34="Aviation",$P$59:$W$61,$A34="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" si="22"/>
         <v>NE</v>
       </c>
       <c r="J34" s="12">
-        <f>C34*D34*F34/1000</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K34" s="12">
-        <f>C34*D34*G34/1000</f>
+        <f t="shared" si="24"/>
         <v>4.2460000000000006E-3</v>
       </c>
       <c r="L34" s="12">
-        <f>C34*D34*H34/1000</f>
+        <f t="shared" si="25"/>
         <v>0.21230000000000002</v>
       </c>
       <c r="M34" s="12" t="e">
-        <f>C34*D34*I34/1000</f>
+        <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
       <c r="N34" s="12"/>
@@ -2073,43 +2242,43 @@
         <v>12</v>
       </c>
       <c r="D35" s="12">
-        <f>IF(ISBLANK(A35), "", VLOOKUP($B35, _xlfn.IFS($A35="Cars and light commercial vehicles", $P$36:$W$43,$A35="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A35="Light duty vehicles",$P$49:$W$50,$A35="Heavy duty vehicles",$P$51:$W$58,$A35="Aviation",$P$59:$W$61,$A35="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="17"/>
         <v>23.4</v>
       </c>
       <c r="E35" s="12" t="str">
-        <f>IF(ISBLANK(B35), "", VLOOKUP($B35, _xlfn.IFS($A35="Cars and light commercial vehicles", $P$36:$W$43,$A35="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A35="Light duty vehicles",$P$49:$W$50,$A35="Heavy duty vehicles",$P$51:$W$58,$A35="Aviation",$P$59:$W$61,$A35="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="18"/>
         <v>GJ/kL</v>
       </c>
       <c r="F35" s="12">
-        <f>IF(ISBLANK(C35), "", VLOOKUP($B35, _xlfn.IFS($A35="Cars and light commercial vehicles", $P$36:$W$43,$A35="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A35="Light duty vehicles",$P$49:$W$50,$A35="Heavy duty vehicles",$P$51:$W$58,$A35="Aviation",$P$59:$W$61,$A35="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G35" s="12">
-        <f>IF(ISBLANK(D35), "", VLOOKUP($B35, _xlfn.IFS($A35="Cars and light commercial vehicles", $P$36:$W$43,$A35="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A35="Light duty vehicles",$P$49:$W$50,$A35="Heavy duty vehicles",$P$51:$W$58,$A35="Aviation",$P$59:$W$61,$A35="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="20"/>
         <v>0.8</v>
       </c>
       <c r="H35" s="12">
-        <f>IF(ISBLANK(E35), "", VLOOKUP($B35, _xlfn.IFS($A35="Cars and light commercial vehicles", $P$36:$W$43,$A35="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A35="Light duty vehicles",$P$49:$W$50,$A35="Heavy duty vehicles",$P$51:$W$58,$A35="Aviation",$P$59:$W$61,$A35="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="21"/>
         <v>1.7</v>
       </c>
       <c r="I35" s="12" t="str">
-        <f>IF(ISBLANK(F35), "", VLOOKUP($B35, _xlfn.IFS($A35="Cars and light commercial vehicles", $P$36:$W$43,$A35="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A35="Light duty vehicles",$P$49:$W$50,$A35="Heavy duty vehicles",$P$51:$W$58,$A35="Aviation",$P$59:$W$61,$A35="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" si="22"/>
         <v>NE</v>
       </c>
       <c r="J35" s="12">
-        <f>C35*D35*F35/1000</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K35" s="12">
-        <f>C35*D35*G35/1000</f>
+        <f t="shared" si="24"/>
         <v>0.22463999999999998</v>
       </c>
       <c r="L35" s="12">
-        <f>C35*D35*H35/1000</f>
+        <f t="shared" si="25"/>
         <v>0.4773599999999999</v>
       </c>
       <c r="M35" s="12" t="e">
-        <f>C35*D35*I35/1000</f>
+        <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
       <c r="N35" s="12"/>
@@ -2123,7 +2292,7 @@
         <v>17</v>
       </c>
       <c r="R35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>40</v>
@@ -2146,49 +2315,49 @@
         <v>14</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36">
         <v>11</v>
       </c>
       <c r="D36" s="12">
-        <f>IF(ISBLANK(A36), "", VLOOKUP($B36, _xlfn.IFS($A36="Cars and light commercial vehicles", $P$36:$W$43,$A36="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A36="Light duty vehicles",$P$49:$W$50,$A36="Heavy duty vehicles",$P$51:$W$58,$A36="Aviation",$P$59:$W$61,$A36="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="17"/>
         <v>38.6</v>
       </c>
       <c r="E36" s="12" t="str">
-        <f>IF(ISBLANK(B36), "", VLOOKUP($B36, _xlfn.IFS($A36="Cars and light commercial vehicles", $P$36:$W$43,$A36="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A36="Light duty vehicles",$P$49:$W$50,$A36="Heavy duty vehicles",$P$51:$W$58,$A36="Aviation",$P$59:$W$61,$A36="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="18"/>
         <v>GJ/kL</v>
       </c>
       <c r="F36" s="12">
-        <f>IF(ISBLANK(C36), "", VLOOKUP($B36, _xlfn.IFS($A36="Cars and light commercial vehicles", $P$36:$W$43,$A36="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A36="Light duty vehicles",$P$49:$W$50,$A36="Heavy duty vehicles",$P$51:$W$58,$A36="Aviation",$P$59:$W$61,$A36="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G36" s="12">
-        <f>IF(ISBLANK(D36), "", VLOOKUP($B36, _xlfn.IFS($A36="Cars and light commercial vehicles", $P$36:$W$43,$A36="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A36="Light duty vehicles",$P$49:$W$50,$A36="Heavy duty vehicles",$P$51:$W$58,$A36="Aviation",$P$59:$W$61,$A36="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="20"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="H36" s="12">
-        <f>IF(ISBLANK(E36), "", VLOOKUP($B36, _xlfn.IFS($A36="Cars and light commercial vehicles", $P$36:$W$43,$A36="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A36="Light duty vehicles",$P$49:$W$50,$A36="Heavy duty vehicles",$P$51:$W$58,$A36="Aviation",$P$59:$W$61,$A36="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="21"/>
         <v>0.4</v>
       </c>
       <c r="I36" s="12" t="str">
-        <f>IF(ISBLANK(F36), "", VLOOKUP($B36, _xlfn.IFS($A36="Cars and light commercial vehicles", $P$36:$W$43,$A36="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A36="Light duty vehicles",$P$49:$W$50,$A36="Heavy duty vehicles",$P$51:$W$58,$A36="Aviation",$P$59:$W$61,$A36="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" si="22"/>
         <v>NE</v>
       </c>
       <c r="J36" s="12">
-        <f>C36*D36*F36/1000</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K36" s="12">
-        <f>C36*D36*G36/1000</f>
+        <f t="shared" si="24"/>
         <v>2.9722000000000005E-2</v>
       </c>
       <c r="L36" s="12">
-        <f>C36*D36*H36/1000</f>
+        <f t="shared" si="25"/>
         <v>0.16984000000000002</v>
       </c>
       <c r="M36" s="12" t="e">
-        <f>C36*D36*I36/1000</f>
+        <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
       <c r="N36" s="12"/>
@@ -2202,7 +2371,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="R36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S36" s="2">
         <v>67.400000000000006</v>
@@ -2225,49 +2394,49 @@
         <v>14</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>12</v>
       </c>
       <c r="D37" s="12">
-        <f>IF(ISBLANK(A37), "", VLOOKUP($B37, _xlfn.IFS($A37="Cars and light commercial vehicles", $P$36:$W$43,$A37="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A37="Light duty vehicles",$P$49:$W$50,$A37="Heavy duty vehicles",$P$51:$W$58,$A37="Aviation",$P$59:$W$61,$A37="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="17"/>
         <v>38.6</v>
       </c>
       <c r="E37" s="12" t="str">
-        <f>IF(ISBLANK(B37), "", VLOOKUP($B37, _xlfn.IFS($A37="Cars and light commercial vehicles", $P$36:$W$43,$A37="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A37="Light duty vehicles",$P$49:$W$50,$A37="Heavy duty vehicles",$P$51:$W$58,$A37="Aviation",$P$59:$W$61,$A37="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="18"/>
         <v>GJ/kL</v>
       </c>
       <c r="F37" s="12">
-        <f>IF(ISBLANK(C37), "", VLOOKUP($B37, _xlfn.IFS($A37="Cars and light commercial vehicles", $P$36:$W$43,$A37="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A37="Light duty vehicles",$P$49:$W$50,$A37="Heavy duty vehicles",$P$51:$W$58,$A37="Aviation",$P$59:$W$61,$A37="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G37" s="12">
-        <f>IF(ISBLANK(D37), "", VLOOKUP($B37, _xlfn.IFS($A37="Cars and light commercial vehicles", $P$36:$W$43,$A37="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A37="Light duty vehicles",$P$49:$W$50,$A37="Heavy duty vehicles",$P$51:$W$58,$A37="Aviation",$P$59:$W$61,$A37="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="20"/>
         <v>0.1</v>
       </c>
       <c r="H37" s="12">
-        <f>IF(ISBLANK(E37), "", VLOOKUP($B37, _xlfn.IFS($A37="Cars and light commercial vehicles", $P$36:$W$43,$A37="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A37="Light duty vehicles",$P$49:$W$50,$A37="Heavy duty vehicles",$P$51:$W$58,$A37="Aviation",$P$59:$W$61,$A37="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="21"/>
         <v>0.4</v>
       </c>
       <c r="I37" s="12" t="str">
-        <f>IF(ISBLANK(F37), "", VLOOKUP($B37, _xlfn.IFS($A37="Cars and light commercial vehicles", $P$36:$W$43,$A37="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A37="Light duty vehicles",$P$49:$W$50,$A37="Heavy duty vehicles",$P$51:$W$58,$A37="Aviation",$P$59:$W$61,$A37="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" si="22"/>
         <v>NE</v>
       </c>
       <c r="J37" s="12">
-        <f>C37*D37*F37/1000</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K37" s="12">
-        <f>C37*D37*G37/1000</f>
+        <f t="shared" si="24"/>
         <v>4.6320000000000007E-2</v>
       </c>
       <c r="L37" s="12">
-        <f>C37*D37*H37/1000</f>
+        <f t="shared" si="25"/>
         <v>0.18528000000000003</v>
       </c>
       <c r="M37" s="12" t="e">
-        <f>C37*D37*I37/1000</f>
+        <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
       <c r="N37" s="12"/>
@@ -2281,7 +2450,7 @@
         <v>38.6</v>
       </c>
       <c r="R37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S37">
         <v>69.900000000000006</v>
@@ -2304,49 +2473,49 @@
         <v>14</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38">
         <v>13</v>
       </c>
       <c r="D38" s="12">
-        <f>IF(ISBLANK(A38), "", VLOOKUP($B38, _xlfn.IFS($A38="Cars and light commercial vehicles", $P$36:$W$43,$A38="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A38="Light duty vehicles",$P$49:$W$50,$A38="Heavy duty vehicles",$P$51:$W$58,$A38="Aviation",$P$59:$W$61,$A38="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="17"/>
         <v>38.6</v>
       </c>
       <c r="E38" s="12" t="str">
-        <f>IF(ISBLANK(B38), "", VLOOKUP($B38, _xlfn.IFS($A38="Cars and light commercial vehicles", $P$36:$W$43,$A38="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A38="Light duty vehicles",$P$49:$W$50,$A38="Heavy duty vehicles",$P$51:$W$58,$A38="Aviation",$P$59:$W$61,$A38="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="18"/>
         <v>GJ/kL</v>
       </c>
       <c r="F38" s="12">
-        <f>IF(ISBLANK(C38), "", VLOOKUP($B38, _xlfn.IFS($A38="Cars and light commercial vehicles", $P$36:$W$43,$A38="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A38="Light duty vehicles",$P$49:$W$50,$A38="Heavy duty vehicles",$P$51:$W$58,$A38="Aviation",$P$59:$W$61,$A38="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G38" s="12">
-        <f>IF(ISBLANK(D38), "", VLOOKUP($B38, _xlfn.IFS($A38="Cars and light commercial vehicles", $P$36:$W$43,$A38="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A38="Light duty vehicles",$P$49:$W$50,$A38="Heavy duty vehicles",$P$51:$W$58,$A38="Aviation",$P$59:$W$61,$A38="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="20"/>
         <v>0.2</v>
       </c>
       <c r="H38" s="12">
-        <f>IF(ISBLANK(E38), "", VLOOKUP($B38, _xlfn.IFS($A38="Cars and light commercial vehicles", $P$36:$W$43,$A38="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A38="Light duty vehicles",$P$49:$W$50,$A38="Heavy duty vehicles",$P$51:$W$58,$A38="Aviation",$P$59:$W$61,$A38="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="21"/>
         <v>0.4</v>
       </c>
       <c r="I38" s="12" t="str">
-        <f>IF(ISBLANK(F38), "", VLOOKUP($B38, _xlfn.IFS($A38="Cars and light commercial vehicles", $P$36:$W$43,$A38="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A38="Light duty vehicles",$P$49:$W$50,$A38="Heavy duty vehicles",$P$51:$W$58,$A38="Aviation",$P$59:$W$61,$A38="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" si="22"/>
         <v>NE</v>
       </c>
       <c r="J38" s="12">
-        <f>C38*D38*F38/1000</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K38" s="12">
-        <f>C38*D38*G38/1000</f>
+        <f t="shared" si="24"/>
         <v>0.10036000000000002</v>
       </c>
       <c r="L38" s="12">
-        <f>C38*D38*H38/1000</f>
+        <f t="shared" si="25"/>
         <v>0.20072000000000004</v>
       </c>
       <c r="M38" s="12" t="e">
-        <f>C38*D38*I38/1000</f>
+        <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
       <c r="N38" s="12"/>
@@ -2360,7 +2529,7 @@
         <v>26.2</v>
       </c>
       <c r="R38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S38" s="2">
         <v>60.2</v>
@@ -2389,43 +2558,43 @@
         <v>10</v>
       </c>
       <c r="D39" s="12">
-        <f>IF(ISBLANK(A39), "", VLOOKUP($B39, _xlfn.IFS($A39="Cars and light commercial vehicles", $P$36:$W$43,$A39="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A39="Light duty vehicles",$P$49:$W$50,$A39="Heavy duty vehicles",$P$51:$W$58,$A39="Aviation",$P$59:$W$61,$A39="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),2,FALSE))</f>
+        <f t="shared" si="17"/>
         <v>36.799999999999997</v>
       </c>
       <c r="E39" s="12" t="str">
-        <f>IF(ISBLANK(B39), "", VLOOKUP($B39, _xlfn.IFS($A39="Cars and light commercial vehicles", $P$36:$W$43,$A39="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A39="Light duty vehicles",$P$49:$W$50,$A39="Heavy duty vehicles",$P$51:$W$58,$A39="Aviation",$P$59:$W$61,$A39="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),3,FALSE))</f>
+        <f t="shared" si="18"/>
         <v>GJ/kL</v>
       </c>
       <c r="F39" s="12">
-        <f>IF(ISBLANK(C39), "", VLOOKUP($B39, _xlfn.IFS($A39="Cars and light commercial vehicles", $P$36:$W$43,$A39="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A39="Light duty vehicles",$P$49:$W$50,$A39="Heavy duty vehicles",$P$51:$W$58,$A39="Aviation",$P$59:$W$61,$A39="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),4,FALSE))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G39" s="12">
-        <f>IF(ISBLANK(D39), "", VLOOKUP($B39, _xlfn.IFS($A39="Cars and light commercial vehicles", $P$36:$W$43,$A39="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A39="Light duty vehicles",$P$49:$W$50,$A39="Heavy duty vehicles",$P$51:$W$58,$A39="Aviation",$P$59:$W$61,$A39="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),5,FALSE))</f>
+        <f t="shared" si="20"/>
         <v>0.01</v>
       </c>
       <c r="H39" s="12">
-        <f>IF(ISBLANK(E39), "", VLOOKUP($B39, _xlfn.IFS($A39="Cars and light commercial vehicles", $P$36:$W$43,$A39="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A39="Light duty vehicles",$P$49:$W$50,$A39="Heavy duty vehicles",$P$51:$W$58,$A39="Aviation",$P$59:$W$61,$A39="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),6,FALSE))</f>
+        <f t="shared" si="21"/>
         <v>0.6</v>
       </c>
       <c r="I39" s="12" t="str">
-        <f>IF(ISBLANK(F39), "", VLOOKUP($B39, _xlfn.IFS($A39="Cars and light commercial vehicles", $P$36:$W$43,$A39="Cars and light commercial vehicles (pre 2004)", $P$44:$W$48,$A39="Light duty vehicles",$P$49:$W$50,$A39="Heavy duty vehicles",$P$51:$W$58,$A39="Aviation",$P$59:$W$61,$A39="Vessel",$P$63:$W$65,TRUE,$P$66:$W$66),8,FALSE))</f>
+        <f t="shared" si="22"/>
         <v>NE</v>
       </c>
       <c r="J39" s="12">
-        <f>C39*D39*F39/1000</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K39" s="12">
-        <f>C39*D39*G39/1000</f>
+        <f t="shared" si="24"/>
         <v>3.6800000000000001E-3</v>
       </c>
       <c r="L39" s="12">
-        <f>C39*D39*H39/1000</f>
+        <f t="shared" si="25"/>
         <v>0.2208</v>
       </c>
       <c r="M39" s="12" t="e">
-        <f>C39*D39*I39/1000</f>
+        <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
       <c r="N39" s="12"/>
@@ -2439,7 +2608,7 @@
         <v>39.700000000000003</v>
       </c>
       <c r="R39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S39" s="2">
         <v>73.599999999999994</v>
@@ -2479,7 +2648,7 @@
         <v>23.4</v>
       </c>
       <c r="R40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S40" s="2">
         <v>0</v>
@@ -2519,7 +2688,7 @@
         <v>34.6</v>
       </c>
       <c r="R41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S41" s="2">
         <v>0</v>
@@ -2559,7 +2728,7 @@
         <v>38.6</v>
       </c>
       <c r="R42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S42" s="11">
         <v>0</v>
@@ -2590,7 +2759,7 @@
         <v>23.4</v>
       </c>
       <c r="R43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S43" s="11">
         <v>0</v>
@@ -2612,7 +2781,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="O44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P44" t="s">
         <v>19</v>
@@ -2621,7 +2790,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="R44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S44" s="2">
         <v>67.400000000000006</v>
@@ -2633,7 +2802,8 @@
         <v>1.6</v>
       </c>
       <c r="V44">
-        <v>67.62</v>
+        <f>SUM(S44:U44)</f>
+        <v>69.599999999999994</v>
       </c>
       <c r="W44">
         <v>17.2</v>
@@ -2643,7 +2813,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="O45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P45" t="s">
         <v>20</v>
@@ -2652,7 +2822,7 @@
         <v>38.6</v>
       </c>
       <c r="R45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S45">
         <v>69.900000000000006</v>
@@ -2664,7 +2834,8 @@
         <v>0.4</v>
       </c>
       <c r="V45">
-        <v>70.41</v>
+        <f t="shared" ref="V45:V48" si="27">SUM(S45:U45)</f>
+        <v>70.400000000000006</v>
       </c>
       <c r="W45">
         <v>17.3</v>
@@ -2674,7 +2845,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="O46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P46" t="s">
         <v>21</v>
@@ -2683,7 +2854,7 @@
         <v>26.2</v>
       </c>
       <c r="R46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S46" s="2">
         <v>60.2</v>
@@ -2695,7 +2866,8 @@
         <v>0.6</v>
       </c>
       <c r="V46">
-        <v>61</v>
+        <f t="shared" si="27"/>
+        <v>61.500000000000007</v>
       </c>
       <c r="W46">
         <v>20.2</v>
@@ -2705,7 +2877,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="O47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P47" t="s">
         <v>23</v>
@@ -2714,7 +2886,7 @@
         <v>23.4</v>
       </c>
       <c r="R47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S47" s="2">
         <v>0</v>
@@ -2725,8 +2897,9 @@
       <c r="U47">
         <v>1.7</v>
       </c>
-      <c r="V47" s="7">
-        <v>0.4</v>
+      <c r="V47">
+        <f t="shared" si="27"/>
+        <v>2.5</v>
       </c>
       <c r="W47" t="s">
         <v>10</v>
@@ -2736,7 +2909,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="O48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -2745,7 +2918,7 @@
         <v>38.6</v>
       </c>
       <c r="R48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S48" s="11">
         <v>0</v>
@@ -2756,8 +2929,9 @@
       <c r="U48" s="10">
         <v>0.4</v>
       </c>
-      <c r="V48" s="10">
-        <v>0.51</v>
+      <c r="V48">
+        <f t="shared" si="27"/>
+        <v>0.5</v>
       </c>
       <c r="W48" s="10" t="s">
         <v>10</v>
@@ -2776,7 +2950,7 @@
         <v>3.9300000000000002E-2</v>
       </c>
       <c r="R49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S49" s="11">
         <v>51.4</v>
@@ -2807,7 +2981,7 @@
         <v>25.3</v>
       </c>
       <c r="R50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S50" s="11">
         <v>51.4</v>
@@ -2838,7 +3012,7 @@
         <v>3.9300000000000002E-2</v>
       </c>
       <c r="R51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S51" s="11">
         <v>51.4</v>
@@ -2869,7 +3043,7 @@
         <v>25.3</v>
       </c>
       <c r="R52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S52" s="11">
         <v>51.4</v>
@@ -2900,7 +3074,7 @@
         <v>38.6</v>
       </c>
       <c r="R53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S53" s="11">
         <v>69.900000000000006</v>
@@ -2931,7 +3105,7 @@
         <v>38.6</v>
       </c>
       <c r="R54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S54" s="11">
         <v>69.900000000000006</v>
@@ -2962,7 +3136,7 @@
         <v>38.6</v>
       </c>
       <c r="R55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S55" s="11">
         <v>69.900000000000006</v>
@@ -2987,13 +3161,13 @@
         <v>14</v>
       </c>
       <c r="P56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q56" s="2">
         <v>38.6</v>
       </c>
       <c r="R56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S56" s="11">
         <v>0</v>
@@ -3018,13 +3192,13 @@
         <v>14</v>
       </c>
       <c r="P57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q57" s="2">
         <v>38.6</v>
       </c>
       <c r="R57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S57" s="11">
         <v>0</v>
@@ -3049,13 +3223,13 @@
         <v>14</v>
       </c>
       <c r="P58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q58" s="2">
         <v>38.6</v>
       </c>
       <c r="R58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S58" s="11">
         <v>0</v>
@@ -3086,7 +3260,7 @@
         <v>33.1</v>
       </c>
       <c r="R59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S59" s="11">
         <v>67</v>
@@ -3117,7 +3291,7 @@
         <v>36.799999999999997</v>
       </c>
       <c r="R60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S60" s="11">
         <v>69.599999999999994</v>
@@ -3148,7 +3322,7 @@
         <v>36.799999999999997</v>
       </c>
       <c r="R61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S61" s="11">
         <v>0</v>
@@ -3189,7 +3363,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="R63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S63" s="9">
         <v>67.400000000000006</v>
@@ -3199,6 +3373,10 @@
       </c>
       <c r="U63" s="9">
         <v>0.3</v>
+      </c>
+      <c r="V63" s="17">
+        <f>SUM(S63:U63)</f>
+        <v>77.8</v>
       </c>
       <c r="W63" s="9">
         <v>17.2</v>
@@ -3217,7 +3395,7 @@
         <v>38.6</v>
       </c>
       <c r="R64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S64" s="2">
         <v>69.900000000000006</v>
@@ -3227,6 +3405,10 @@
       </c>
       <c r="U64" s="10">
         <v>0.5</v>
+      </c>
+      <c r="V64" s="17">
+        <f t="shared" ref="V64:V66" si="28">SUM(S64:U64)</f>
+        <v>70.600000000000009</v>
       </c>
       <c r="W64">
         <v>17.3</v>
@@ -3245,7 +3427,7 @@
         <v>39.700000000000003</v>
       </c>
       <c r="R65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S65" s="2">
         <v>73.599999999999994</v>
@@ -3255,6 +3437,10 @@
       </c>
       <c r="U65">
         <v>0.5</v>
+      </c>
+      <c r="V65" s="17">
+        <f t="shared" si="28"/>
+        <v>74.3</v>
       </c>
       <c r="W65">
         <v>18</v>
@@ -3271,7 +3457,7 @@
         <v>38.6</v>
       </c>
       <c r="R66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S66" s="2">
         <v>69.900000000000006</v>
@@ -3281,6 +3467,10 @@
       </c>
       <c r="U66">
         <v>0.5</v>
+      </c>
+      <c r="V66" s="17">
+        <f t="shared" si="28"/>
+        <v>70.7</v>
       </c>
       <c r="W66">
         <v>17.3</v>

--- a/packages/calculators/src/modules/test/8.1-transport-fuel.xlsx
+++ b/packages/calculators/src/modules/test/8.1-transport-fuel.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AA7B24-05AC-454A-AA21-C567261DF5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51140" yWindow="5260" windowWidth="28800" windowHeight="18980" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
